--- a/data/Excel/GuLiStrikeGameTexts.xlsx
+++ b/data/Excel/GuLiStrikeGameTexts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="427">
   <si>
     <t>文本id</t>
   </si>
@@ -1314,6 +1314,51 @@
     <t xml:space="preserve">建造 [B]
 选择建筑图标，再选择建造位置。
 </t>
+  </si>
+  <si>
+    <t>Commander/Behavior/GuLiCommanderAbilityBridge.cpp；界面文案</t>
+  </si>
+  <si>
+    <t>UI.BuildingPlacementComponent.RotateHint</t>
+  </si>
+  <si>
+    <t>建筑放置操作提示</t>
+  </si>
+  <si>
+    <t>R：旋转90°</t>
+  </si>
+  <si>
+    <t>UI.Performance.FPSPending</t>
+  </si>
+  <si>
+    <t>Commander/Presentation/GuLiCommanderHUD.cpp；本地性能指标</t>
+  </si>
+  <si>
+    <t>FPS --</t>
+  </si>
+  <si>
+    <t>UI.Performance.FPS</t>
+  </si>
+  <si>
+    <t>FPS {0}</t>
+  </si>
+  <si>
+    <t>UI.Performance.LatencyPending</t>
+  </si>
+  <si>
+    <t>延迟 --</t>
+  </si>
+  <si>
+    <t>UI.Performance.LatencyLocal</t>
+  </si>
+  <si>
+    <t>延迟 本地</t>
+  </si>
+  <si>
+    <t>UI.Performance.LatencyRTT</t>
+  </si>
+  <si>
+    <t>延迟 {0} ms (RTT)</t>
   </si>
 </sst>
 </file>
@@ -3075,7 +3120,7 @@
         <v>271</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>273</v>
@@ -3086,7 +3131,7 @@
         <v>274</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>275</v>
@@ -3097,7 +3142,7 @@
         <v>276</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>277</v>
@@ -3108,7 +3153,7 @@
         <v>278</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>279</v>
@@ -3119,7 +3164,7 @@
         <v>280</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>281</v>
@@ -3708,6 +3753,72 @@
         <v>394</v>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>413</v>
+      </c>
+      <c r="B189" t="s">
+        <v>414</v>
+      </c>
+      <c r="C189" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>416</v>
+      </c>
+      <c r="B190" t="s">
+        <v>417</v>
+      </c>
+      <c r="C190" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>419</v>
+      </c>
+      <c r="B191" t="s">
+        <v>417</v>
+      </c>
+      <c r="C191" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>421</v>
+      </c>
+      <c r="B192" t="s">
+        <v>417</v>
+      </c>
+      <c r="C192" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>423</v>
+      </c>
+      <c r="B193" t="s">
+        <v>417</v>
+      </c>
+      <c r="C193" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>425</v>
+      </c>
+      <c r="B194" t="s">
+        <v>417</v>
+      </c>
+      <c r="C194" t="s">
+        <v>426</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeGameTexts.xlsx
+++ b/data/Excel/GuLiStrikeGameTexts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
   <si>
     <t>文本id</t>
   </si>
@@ -1359,6 +1359,117 @@
   </si>
   <si>
     <t>延迟 {0} ms (RTT)</t>
+  </si>
+  <si>
+    <t>Card.WM01.FireRate.Title</t>
+  </si>
+  <si>
+    <t>战争机器肉鸽卡标题</t>
+  </si>
+  <si>
+    <t>增加射速</t>
+  </si>
+  <si>
+    <t>Card.WM01.FireRate.Description</t>
+  </si>
+  <si>
+    <t>战争机器肉鸽卡说明；{0}来自BonusPercent×100</t>
+  </si>
+  <si>
+    <t>战争机器的普攻射速提高 {0}%。</t>
+  </si>
+  <si>
+    <t>Card.WM01.HighSpeed.Title</t>
+  </si>
+  <si>
+    <t>极速机动</t>
+  </si>
+  <si>
+    <t>Card.WM01.HighSpeed.Description</t>
+  </si>
+  <si>
+    <t>战争机器的移动速度提高 {0}%。</t>
+  </si>
+  <si>
+    <t>Card.WM01.MissileDamage.Title</t>
+  </si>
+  <si>
+    <t>增加导弹伤害</t>
+  </si>
+  <si>
+    <t>Card.WM01.MissileDamage.Description</t>
+  </si>
+  <si>
+    <t>战争机器的导弹伤害提高 {0}%。</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Title</t>
+  </si>
+  <si>
+    <t>实战选牌界面</t>
+  </si>
+  <si>
+    <t>命运之选</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Entering</t>
+  </si>
+  <si>
+    <t>卡牌入场中…</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Choose</t>
+  </si>
+  <si>
+    <t>移动鼠标轻压牌面 · 单击选择 · Esc 取消</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Flip</t>
+  </si>
+  <si>
+    <t>翻牌中…</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Confirm</t>
+  </si>
+  <si>
+    <t>再次点击所选卡牌确认 · Esc 取消</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Submitting</t>
+  </si>
+  <si>
+    <t>正在确认加成…</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Success</t>
+  </si>
+  <si>
+    <t>加成已生效</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Failed</t>
+  </si>
+  <si>
+    <t>选牌失败：{0} · Esc 返回战场</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.OpenFailed</t>
+  </si>
+  <si>
+    <t>无法打开选牌：{0}</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Replay</t>
+  </si>
+  <si>
+    <t>重新播放</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Done</t>
+  </si>
+  <si>
+    <t>选择完成</t>
   </si>
 </sst>
 </file>
@@ -3819,6 +3930,193 @@
         <v>426</v>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>427</v>
+      </c>
+      <c r="B195" t="s">
+        <v>428</v>
+      </c>
+      <c r="C195" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>430</v>
+      </c>
+      <c r="B196" t="s">
+        <v>431</v>
+      </c>
+      <c r="C196" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>433</v>
+      </c>
+      <c r="B197" t="s">
+        <v>428</v>
+      </c>
+      <c r="C197" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>435</v>
+      </c>
+      <c r="B198" t="s">
+        <v>431</v>
+      </c>
+      <c r="C198" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>437</v>
+      </c>
+      <c r="B199" t="s">
+        <v>428</v>
+      </c>
+      <c r="C199" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>439</v>
+      </c>
+      <c r="B200" t="s">
+        <v>431</v>
+      </c>
+      <c r="C200" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>441</v>
+      </c>
+      <c r="B201" t="s">
+        <v>442</v>
+      </c>
+      <c r="C201" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>444</v>
+      </c>
+      <c r="B202" t="s">
+        <v>442</v>
+      </c>
+      <c r="C202" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>446</v>
+      </c>
+      <c r="B203" t="s">
+        <v>442</v>
+      </c>
+      <c r="C203" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>448</v>
+      </c>
+      <c r="B204" t="s">
+        <v>442</v>
+      </c>
+      <c r="C204" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>450</v>
+      </c>
+      <c r="B205" t="s">
+        <v>442</v>
+      </c>
+      <c r="C205" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>452</v>
+      </c>
+      <c r="B206" t="s">
+        <v>442</v>
+      </c>
+      <c r="C206" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>454</v>
+      </c>
+      <c r="B207" t="s">
+        <v>442</v>
+      </c>
+      <c r="C207" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>456</v>
+      </c>
+      <c r="B208" t="s">
+        <v>442</v>
+      </c>
+      <c r="C208" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>458</v>
+      </c>
+      <c r="B209" t="s">
+        <v>442</v>
+      </c>
+      <c r="C209" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>460</v>
+      </c>
+      <c r="B210" t="s">
+        <v>442</v>
+      </c>
+      <c r="C210" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>462</v>
+      </c>
+      <c r="B211" t="s">
+        <v>442</v>
+      </c>
+      <c r="C211" t="s">
+        <v>463</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeGameTexts.xlsx
+++ b/data/Excel/GuLiStrikeGameTexts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
   <si>
     <t>文本id</t>
   </si>
@@ -1470,6 +1470,183 @@
   </si>
   <si>
     <t>选择完成</t>
+  </si>
+  <si>
+    <t>UI.Camera.GroundDistances</t>
+  </si>
+  <si>
+    <t>指挥官只读距离采样；参数为垂直离地高度及画面中心地面距离</t>
+  </si>
+  <si>
+    <t>离地高度 {0}  |  中心地面距离 {1}</t>
+  </si>
+  <si>
+    <t>UI.Camera.Meters</t>
+  </si>
+  <si>
+    <t>指挥官距离数值；米，保留一位小数</t>
+  </si>
+  <si>
+    <t>{0} 米</t>
+  </si>
+  <si>
+    <t>UI.Camera.NoGround</t>
+  </si>
+  <si>
+    <t>摄像机正下方无地形或中心射线未命中地形</t>
+  </si>
+  <si>
+    <t>无地形</t>
+  </si>
+  <si>
+    <t>重防号肉鸽卡标题</t>
+  </si>
+  <si>
+    <t>重防号肉鸽卡说明；{0}来自BonusPercent×100</t>
+  </si>
+  <si>
+    <t>重防号的普攻射速提高 {0}%。</t>
+  </si>
+  <si>
+    <t>重防号的移动速度提高 {0}%。</t>
+  </si>
+  <si>
+    <t>重防号的导弹伤害提高 {0}%。</t>
+  </si>
+  <si>
+    <t>Card.WM01.MissilePod.Title</t>
+  </si>
+  <si>
+    <t>重防导弹仓</t>
+  </si>
+  <si>
+    <t>Card.WM01.MissilePod.Description</t>
+  </si>
+  <si>
+    <t>重防号导弹槽解锁；无数值占位符</t>
+  </si>
+  <si>
+    <t>为本队所有重防号装配导弹仓，解锁导弹技能。每局仅可获取一次。</t>
+  </si>
+  <si>
+    <t>Card.WM01.RainSalvo.Title</t>
+  </si>
+  <si>
+    <t>雨点攻势</t>
+  </si>
+  <si>
+    <t>Card.WM01.RainSalvo.Description</t>
+  </si>
+  <si>
+    <t>重防号肉鸽卡说明；{0}来自BonusCount</t>
+  </si>
+  <si>
+    <t>重防号每次释放导弹技能时额外齐射 {0} 枚导弹。可重复叠加。</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Empty</t>
+  </si>
+  <si>
+    <t>无合格候选卡时显示</t>
+  </si>
+  <si>
+    <t>暂无可选牌</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.AcquisitionLimit</t>
+  </si>
+  <si>
+    <t>结算复核：达到获取次数</t>
+  </si>
+  <si>
+    <t>该卡已达到本局获取上限</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.RequirementNotMet</t>
+  </si>
+  <si>
+    <t>结算复核：缺少依赖</t>
+  </si>
+  <si>
+    <t>尚未获得该卡要求的前置卡牌</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Excluded</t>
+  </si>
+  <si>
+    <t>结算复核：双向互斥</t>
+  </si>
+  <si>
+    <t>该卡与本队已获得的卡牌互斥</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Reroll</t>
+  </si>
+  <si>
+    <t>F4选牌重选按钮</t>
+  </si>
+  <si>
+    <t>重选</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.Rerolling</t>
+  </si>
+  <si>
+    <t>F4选牌等待重选结果</t>
+  </si>
+  <si>
+    <t>正在重选…</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.RerollHint</t>
+  </si>
+  <si>
+    <t>F4重选按钮说明</t>
+  </si>
+  <si>
+    <t>免费重新随机可选卡牌，优先换成当前未显示的牌。</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.NoAlternatives</t>
+  </si>
+  <si>
+    <t>没有其他合格卡时保留当前选择</t>
+  </si>
+  <si>
+    <t>暂无其他可选卡牌</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.RerollUnavailable</t>
+  </si>
+  <si>
+    <t>重选会话过期或已提交</t>
+  </si>
+  <si>
+    <t>当前无法重选，请重新打开选牌界面</t>
+  </si>
+  <si>
+    <t>UI.RogueCards.RerollBusy</t>
+  </si>
+  <si>
+    <t>重选触发服务器请求限流</t>
+  </si>
+  <si>
+    <t>操作过快，请稍后重选</t>
+  </si>
+  <si>
+    <t>&lt;Unit&gt;重防号&lt;/&gt; &lt;Gain&gt;普攻射速+{0}%&lt;/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Unit&gt;重防号&lt;/&gt; &lt;Gain&gt;移动速度+{0}%&lt;/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Unit&gt;重防号&lt;/&gt; &lt;Gain&gt;导弹伤害+{0}%&lt;/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Unit&gt;重防号&lt;/&gt; 解锁&lt;Gain&gt;导弹技能&lt;/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Unit&gt;重防号&lt;/&gt; &lt;Gain&gt;导弹齐射数量+{0}&lt;/&gt;</t>
   </si>
 </sst>
 </file>
@@ -3935,7 +4112,7 @@
         <v>427</v>
       </c>
       <c r="B195" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="C195" t="s">
         <v>429</v>
@@ -3946,10 +4123,10 @@
         <v>430</v>
       </c>
       <c r="B196" t="s">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="C196" t="s">
-        <v>432</v>
+        <v>518</v>
       </c>
     </row>
     <row r="197">
@@ -3957,7 +4134,7 @@
         <v>433</v>
       </c>
       <c r="B197" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="C197" t="s">
         <v>434</v>
@@ -3968,10 +4145,10 @@
         <v>435</v>
       </c>
       <c r="B198" t="s">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="C198" t="s">
-        <v>436</v>
+        <v>519</v>
       </c>
     </row>
     <row r="199">
@@ -3979,7 +4156,7 @@
         <v>437</v>
       </c>
       <c r="B199" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="C199" t="s">
         <v>438</v>
@@ -3990,10 +4167,10 @@
         <v>439</v>
       </c>
       <c r="B200" t="s">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="C200" t="s">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="201">
@@ -4117,6 +4294,193 @@
         <v>463</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>464</v>
+      </c>
+      <c r="B212" t="s">
+        <v>465</v>
+      </c>
+      <c r="C212" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>467</v>
+      </c>
+      <c r="B213" t="s">
+        <v>468</v>
+      </c>
+      <c r="C213" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>470</v>
+      </c>
+      <c r="B214" t="s">
+        <v>471</v>
+      </c>
+      <c r="C214" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>478</v>
+      </c>
+      <c r="B215" t="s">
+        <v>473</v>
+      </c>
+      <c r="C215" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>480</v>
+      </c>
+      <c r="B216" t="s">
+        <v>481</v>
+      </c>
+      <c r="C216" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>483</v>
+      </c>
+      <c r="B217" t="s">
+        <v>473</v>
+      </c>
+      <c r="C217" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>485</v>
+      </c>
+      <c r="B218" t="s">
+        <v>486</v>
+      </c>
+      <c r="C218" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>488</v>
+      </c>
+      <c r="B219" t="s">
+        <v>489</v>
+      </c>
+      <c r="C219" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>491</v>
+      </c>
+      <c r="B220" t="s">
+        <v>492</v>
+      </c>
+      <c r="C220" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>494</v>
+      </c>
+      <c r="B221" t="s">
+        <v>495</v>
+      </c>
+      <c r="C221" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>497</v>
+      </c>
+      <c r="B222" t="s">
+        <v>498</v>
+      </c>
+      <c r="C222" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>500</v>
+      </c>
+      <c r="B223" t="s">
+        <v>501</v>
+      </c>
+      <c r="C223" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>503</v>
+      </c>
+      <c r="B224" t="s">
+        <v>504</v>
+      </c>
+      <c r="C224" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>506</v>
+      </c>
+      <c r="B225" t="s">
+        <v>507</v>
+      </c>
+      <c r="C225" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>509</v>
+      </c>
+      <c r="B226" t="s">
+        <v>510</v>
+      </c>
+      <c r="C226" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>512</v>
+      </c>
+      <c r="B227" t="s">
+        <v>513</v>
+      </c>
+      <c r="C227" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>515</v>
+      </c>
+      <c r="B228" t="s">
+        <v>516</v>
+      </c>
+      <c r="C228" t="s">
+        <v>517</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeGameTexts.xlsx
+++ b/data/Excel/GuLiStrikeGameTexts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
   <si>
     <t>文本id</t>
   </si>
@@ -1647,6 +1647,25 @@
   </si>
   <si>
     <t>&lt;Unit&gt;重防号&lt;/&gt; &lt;Gain&gt;导弹齐射数量+{0}&lt;/&gt;</t>
+  </si>
+  <si>
+    <t>UI.CommanderSkills.GuidanceBatch</t>
+  </si>
+  <si>
+    <t>重防号Q本批导弹及下一Q就绪单位反馈</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> · 本次发射{0}发导弹，{1}台留待下次Q</t>
+  </si>
+  <si>
+    <t>UI.CommanderSkills.PioneerSummon</t>
+  </si>
+  <si>
+    <t>先驱号Q召唤提示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+先驱号：按Q立即在周围召唤5个扫荡者，每台独立冷却30秒，无资源消耗。召唤兵永久可控、可累积、不占生产人口；空间或容量不足时整批失败，冷却保持不变。</t>
   </si>
 </sst>
 </file>
@@ -4481,6 +4500,28 @@
         <v>517</v>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>523</v>
+      </c>
+      <c r="B229" t="s">
+        <v>524</v>
+      </c>
+      <c r="C229" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>526</v>
+      </c>
+      <c r="B230" t="s">
+        <v>527</v>
+      </c>
+      <c r="C230" t="s">
+        <v>528</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeGameTexts.xlsx
+++ b/data/Excel/GuLiStrikeGameTexts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="534">
   <si>
     <t>文本id</t>
   </si>
@@ -1666,6 +1666,21 @@
   <si>
     <t xml:space="preserve">
 先驱号：按Q立即在周围召唤5个扫荡者，每台独立冷却30秒，无资源消耗。召唤兵永久可控、可累积、不占生产人口；空间或容量不足时整批失败，冷却保持不变。</t>
+  </si>
+  <si>
+    <t>UI.BuildingTypes.PopulationLimit</t>
+  </si>
+  <si>
+    <t>彼之矛首轮建造</t>
+  </si>
+  <si>
+    <t>军队人口已满，无法预留彼之矛人口</t>
+  </si>
+  <si>
+    <t>UI.BuildingTypes.BiZhiMao</t>
+  </si>
+  <si>
+    <t>彼之矛</t>
   </si>
 </sst>
 </file>
@@ -4522,6 +4537,28 @@
         <v>528</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>529</v>
+      </c>
+      <c r="B231" t="s">
+        <v>530</v>
+      </c>
+      <c r="C231" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>532</v>
+      </c>
+      <c r="B232" t="s">
+        <v>530</v>
+      </c>
+      <c r="C232" t="s">
+        <v>533</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeGameTexts.xlsx
+++ b/data/Excel/GuLiStrikeGameTexts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="567">
   <si>
     <t>文本id</t>
   </si>
@@ -1681,6 +1681,105 @@
   </si>
   <si>
     <t>彼之矛</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetThroughput</t>
+  </si>
+  <si>
+    <t>当前客户端连接实际累计字节差/真实秒；收+发合计；1KB=1000B，不是配置上限</t>
+  </si>
+  <si>
+    <t>网络 收 {0} KB/s | 发 {1} KB/s | 合计 {2} KB/s</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetPackets</t>
+  </si>
+  <si>
+    <t>当前连接包速率；丢包为UE计数差/秒，并非丢包百分比</t>
+  </si>
+  <si>
+    <t>包 收 {0}/s 发 {1}/s | 丢包 收 {2}/s 发 {3}/s</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetTransport</t>
+  </si>
+  <si>
+    <t>本端发送额度、所有通道可靠bunch待ACK数；欠账=max(QueuedBits,0)/8，非应用队列大小</t>
+  </si>
+  <si>
+    <t>本端额度 {0} KB/s | 可靠待确认 {1} 块 | 欠账 {2} KB</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetFlightReceive</t>
+  </si>
+  <si>
+    <t>解码飞行事件速率及应用载荷；不等于画面播放量；年龄用估计服务器时间，排除bootstrap，可能含时钟误差</t>
+  </si>
+  <si>
+    <t>飞行事件 收 {0}/s | 载荷 {1} KB/s | 平均估龄 {2} ms</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetPIETransport</t>
+  </si>
+  <si>
+    <t>同进程PIE匹配此客户端的服务器连接：下行发送额度、可靠待ACK块数和发送欠账</t>
+  </si>
+  <si>
+    <t>PIE下行额度 {0} KB/s | 可靠待确认 {1} 块 | 欠账 {2} KB</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetPIEFlightQueue</t>
+  </si>
+  <si>
+    <t>同进程PIE中此客户端的飞行应用队列；队首样本时间至服务器当前时间，不等于纯排队时间</t>
+  </si>
+  <si>
+    <t>PIE本连接 飞行待发 {0} 条 | 队首事件年龄 {1} ms</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetPending</t>
+  </si>
+  <si>
+    <t>新建或重连后先等待完整采样区间；未知值不能显示成零</t>
+  </si>
+  <si>
+    <t>网络 收 -- KB/s | 发 -- KB/s | 合计 -- KB/s</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetLocal</t>
+  </si>
+  <si>
+    <t>本面板按客户端ServerConnection统计，本地/服务端视口不显示其他客户端汇总</t>
+  </si>
+  <si>
+    <t>网络：本地视口（无客户端到服务器连接）</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetFlightPending</t>
+  </si>
+  <si>
+    <t>未得到连续两次飞行计数采样</t>
+  </si>
+  <si>
+    <t>飞行事件 收 --/s | 载荷 -- KB/s | 平均估龄 -- ms</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetPIEQueuePending</t>
+  </si>
+  <si>
+    <t>尚未建立此客户端的服务端飞行事件通道</t>
+  </si>
+  <si>
+    <t>PIE本连接 飞行待发 --（等待通道）</t>
+  </si>
+  <si>
+    <t>UI.Performance.NetPIEUnavailable</t>
+  </si>
+  <si>
+    <t>跨进程PIE或身份尚未匹配时，不产生额外RPC取得服务端信息</t>
+  </si>
+  <si>
+    <t>PIE服务端队列 --（需同进程服务端）</t>
   </si>
 </sst>
 </file>
@@ -4559,6 +4658,127 @@
         <v>533</v>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>534</v>
+      </c>
+      <c r="B233" t="s">
+        <v>535</v>
+      </c>
+      <c r="C233" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>537</v>
+      </c>
+      <c r="B234" t="s">
+        <v>538</v>
+      </c>
+      <c r="C234" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>540</v>
+      </c>
+      <c r="B235" t="s">
+        <v>541</v>
+      </c>
+      <c r="C235" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>543</v>
+      </c>
+      <c r="B236" t="s">
+        <v>544</v>
+      </c>
+      <c r="C236" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>546</v>
+      </c>
+      <c r="B237" t="s">
+        <v>547</v>
+      </c>
+      <c r="C237" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>549</v>
+      </c>
+      <c r="B238" t="s">
+        <v>550</v>
+      </c>
+      <c r="C238" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>552</v>
+      </c>
+      <c r="B239" t="s">
+        <v>553</v>
+      </c>
+      <c r="C239" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>555</v>
+      </c>
+      <c r="B240" t="s">
+        <v>556</v>
+      </c>
+      <c r="C240" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>558</v>
+      </c>
+      <c r="B241" t="s">
+        <v>559</v>
+      </c>
+      <c r="C241" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>561</v>
+      </c>
+      <c r="B242" t="s">
+        <v>562</v>
+      </c>
+      <c r="C242" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>564</v>
+      </c>
+      <c r="B243" t="s">
+        <v>565</v>
+      </c>
+      <c r="C243" t="s">
+        <v>566</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>